--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279C194E-8AF8-49F2-B5AD-B814DD15F5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961204E7-0D09-4B59-8EF3-138FCC3003B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="118">
   <si>
     <t>Date</t>
   </si>
@@ -66,139 +66,232 @@
     <t>SM-980</t>
   </si>
   <si>
+    <t>EgyptAir MS-662</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>29-JUL-26</t>
+  </si>
+  <si>
+    <t>SM-976</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-173</t>
+  </si>
+  <si>
+    <t>30-JUL-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-171</t>
+  </si>
+  <si>
+    <t>01-AUG-26</t>
+  </si>
+  <si>
+    <t>SM-454</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-175</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-674</t>
+  </si>
+  <si>
     <t>EgyptAir MS-644</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>SAR</t>
-  </si>
-  <si>
-    <t>29-JUL-26</t>
-  </si>
-  <si>
-    <t>SM-976</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-173</t>
-  </si>
-  <si>
-    <t>30-JUL-26</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-171</t>
-  </si>
-  <si>
-    <t>01-AUG-26</t>
-  </si>
-  <si>
-    <t>SM-454</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-175</t>
+    <t>02-AUG-26</t>
+  </si>
+  <si>
+    <t>SM-968</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-672</t>
+  </si>
+  <si>
+    <t>03-AUG-26</t>
+  </si>
+  <si>
+    <t>SM-480</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>flynas XY-581</t>
+  </si>
+  <si>
+    <t>04-AUG-26</t>
+  </si>
+  <si>
+    <t>05-AUG-26</t>
+  </si>
+  <si>
+    <t>06-AUG-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-177</t>
+  </si>
+  <si>
+    <t>07-AUG-26</t>
+  </si>
+  <si>
+    <t>08-AUG-26</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-668</t>
+  </si>
+  <si>
+    <t>09-AUG-26</t>
+  </si>
+  <si>
+    <t>10-AUG-26</t>
+  </si>
+  <si>
+    <t>12-AUG-26</t>
+  </si>
+  <si>
+    <t>17-AUG-26</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-670</t>
+  </si>
+  <si>
+    <t>19-AUG-26</t>
+  </si>
+  <si>
+    <t>20-AUG-26</t>
+  </si>
+  <si>
+    <t>22-AUG-26</t>
+  </si>
+  <si>
+    <t>25-AUG-26</t>
+  </si>
+  <si>
+    <t>26-AUG-26</t>
+  </si>
+  <si>
+    <t>31-AUG-26</t>
   </si>
   <si>
     <t>EgyptAir MS-666</t>
   </si>
   <si>
-    <t>02-AUG-26</t>
-  </si>
-  <si>
-    <t>SM-968</t>
-  </si>
-  <si>
-    <t>flynas XY-581</t>
-  </si>
-  <si>
-    <t>03-AUG-26</t>
-  </si>
-  <si>
-    <t>SM-480</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>04-AUG-26</t>
-  </si>
-  <si>
-    <t>05-AUG-26</t>
-  </si>
-  <si>
-    <t>06-AUG-26</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-177</t>
-  </si>
-  <si>
-    <t>07-AUG-26</t>
-  </si>
-  <si>
-    <t>08-AUG-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-668</t>
-  </si>
-  <si>
-    <t>09-AUG-26</t>
-  </si>
-  <si>
-    <t>10-AUG-26</t>
-  </si>
-  <si>
-    <t>17-AUG-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-670</t>
-  </si>
-  <si>
-    <t>18-AUG-26</t>
+    <t>04-SEP-26</t>
+  </si>
+  <si>
+    <t>10-SEP-26</t>
+  </si>
+  <si>
+    <t>Saudia SV-307</t>
+  </si>
+  <si>
+    <t>13-SEP-26</t>
+  </si>
+  <si>
+    <t>flyadeal F3-755</t>
+  </si>
+  <si>
+    <t>Nile Air NP-128</t>
+  </si>
+  <si>
+    <t>flynas XY-577</t>
+  </si>
+  <si>
+    <t>14-SEP-26</t>
+  </si>
+  <si>
+    <t>15-SEP-26</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-664</t>
+  </si>
+  <si>
+    <t>17-SEP-26</t>
+  </si>
+  <si>
+    <t>18-SEP-26</t>
+  </si>
+  <si>
+    <t>20-SEP-26</t>
+  </si>
+  <si>
+    <t>flynas XY-567</t>
+  </si>
+  <si>
+    <t>22-SEP-26</t>
+  </si>
+  <si>
+    <t>23-SEP-26</t>
+  </si>
+  <si>
+    <t>25-SEP-26</t>
+  </si>
+  <si>
+    <t>MED</t>
+  </si>
+  <si>
+    <t>flyadeal F3-753</t>
+  </si>
+  <si>
+    <t>Air Arabia Egypt E5-328</t>
+  </si>
+  <si>
+    <t>26-SEP-26</t>
   </si>
   <si>
     <t>flyadeal F3-779</t>
   </si>
   <si>
-    <t>19-AUG-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-662</t>
-  </si>
-  <si>
-    <t>20-AUG-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-672</t>
-  </si>
-  <si>
-    <t>22-AUG-26</t>
-  </si>
-  <si>
-    <t>24-AUG-26</t>
-  </si>
-  <si>
-    <t>25-AUG-26</t>
-  </si>
-  <si>
-    <t>26-AUG-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-674</t>
-  </si>
-  <si>
-    <t>29-AUG-26</t>
-  </si>
-  <si>
-    <t>31-AUG-26</t>
-  </si>
-  <si>
-    <t>01-SEP-26</t>
-  </si>
-  <si>
-    <t>Saudia SV-307</t>
-  </si>
-  <si>
-    <t>03-SEP-26</t>
+    <t>27-SEP-26</t>
+  </si>
+  <si>
+    <t>01-OCT-26</t>
+  </si>
+  <si>
+    <t>02-OCT-26</t>
+  </si>
+  <si>
+    <t>04-OCT-26</t>
+  </si>
+  <si>
+    <t>05-OCT-26</t>
+  </si>
+  <si>
+    <t>07-OCT-26</t>
+  </si>
+  <si>
+    <t>08-OCT-26</t>
+  </si>
+  <si>
+    <t>Saudia SV-305</t>
+  </si>
+  <si>
+    <t>09-OCT-26</t>
+  </si>
+  <si>
+    <t>11-OCT-26</t>
+  </si>
+  <si>
+    <t>13-OCT-26</t>
+  </si>
+  <si>
+    <t>flynas XY-589</t>
+  </si>
+  <si>
+    <t>16-OCT-26</t>
+  </si>
+  <si>
+    <t>18-OCT-26</t>
+  </si>
+  <si>
+    <t>19-OCT-26</t>
   </si>
   <si>
     <t>flynas XY-565</t>
@@ -207,124 +300,7 @@
     <t>flynas XY-583</t>
   </si>
   <si>
-    <t>flynas XY-567</t>
-  </si>
-  <si>
-    <t>07-SEP-26</t>
-  </si>
-  <si>
-    <t>Saudia SV-387</t>
-  </si>
-  <si>
-    <t>09-SEP-26</t>
-  </si>
-  <si>
-    <t>Saudia SV-335</t>
-  </si>
-  <si>
-    <t>10-SEP-26</t>
-  </si>
-  <si>
-    <t>11-SEP-26</t>
-  </si>
-  <si>
-    <t>13-SEP-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-128</t>
-  </si>
-  <si>
-    <t>14-SEP-26</t>
-  </si>
-  <si>
-    <t>15-SEP-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-664</t>
-  </si>
-  <si>
-    <t>17-SEP-26</t>
-  </si>
-  <si>
-    <t>Saudia SV-305</t>
-  </si>
-  <si>
-    <t>20-SEP-26</t>
-  </si>
-  <si>
-    <t>flyadeal F3-755</t>
-  </si>
-  <si>
-    <t>flyadeal F3-753</t>
-  </si>
-  <si>
-    <t>21-SEP-26</t>
-  </si>
-  <si>
-    <t>Saudia SV-383</t>
-  </si>
-  <si>
-    <t>22-SEP-26</t>
-  </si>
-  <si>
-    <t>23-SEP-26</t>
-  </si>
-  <si>
-    <t>25-SEP-26</t>
-  </si>
-  <si>
-    <t>MED</t>
-  </si>
-  <si>
-    <t>26-SEP-26</t>
-  </si>
-  <si>
-    <t>27-SEP-26</t>
-  </si>
-  <si>
-    <t>28-SEP-26</t>
-  </si>
-  <si>
-    <t>30-SEP-26</t>
-  </si>
-  <si>
-    <t>01-OCT-26</t>
-  </si>
-  <si>
-    <t>02-OCT-26</t>
-  </si>
-  <si>
-    <t>04-OCT-26</t>
-  </si>
-  <si>
-    <t>07-OCT-26</t>
-  </si>
-  <si>
-    <t>09-OCT-26</t>
-  </si>
-  <si>
-    <t>11-OCT-26</t>
-  </si>
-  <si>
-    <t>13-OCT-26</t>
-  </si>
-  <si>
-    <t>14-OCT-26</t>
-  </si>
-  <si>
-    <t>15-OCT-26</t>
-  </si>
-  <si>
-    <t>16-OCT-26</t>
-  </si>
-  <si>
-    <t>17-OCT-26</t>
-  </si>
-  <si>
-    <t>18-OCT-26</t>
-  </si>
-  <si>
-    <t>19-OCT-26</t>
+    <t>20-OCT-26</t>
   </si>
   <si>
     <t>21-OCT-26</t>
@@ -333,6 +309,12 @@
     <t>24-OCT-26</t>
   </si>
   <si>
+    <t>25-OCT-26</t>
+  </si>
+  <si>
+    <t>29-OCT-26</t>
+  </si>
+  <si>
     <t>30-OCT-26</t>
   </si>
   <si>
@@ -345,15 +327,12 @@
     <t>02-NOV-26</t>
   </si>
   <si>
-    <t>Air Arabia Egypt E5-328</t>
-  </si>
-  <si>
-    <t>08-NOV-26</t>
-  </si>
-  <si>
     <t>09-NOV-26</t>
   </si>
   <si>
+    <t>Air Arabia Egypt E5-362</t>
+  </si>
+  <si>
     <t>13-NOV-26</t>
   </si>
   <si>
@@ -381,46 +360,25 @@
     <t>23-NOV-26</t>
   </si>
   <si>
+    <t>29-NOV-26</t>
+  </si>
+  <si>
     <t>30-NOV-26</t>
   </si>
   <si>
     <t>07-DEC-26</t>
   </si>
   <si>
-    <t>Air Arabia Egypt E5-362</t>
-  </si>
-  <si>
-    <t>11-DEC-26</t>
-  </si>
-  <si>
-    <t>13-DEC-26</t>
-  </si>
-  <si>
     <t>14-DEC-26</t>
   </si>
   <si>
-    <t>18-DEC-26</t>
-  </si>
-  <si>
     <t>20-DEC-26</t>
   </si>
   <si>
     <t>21-DEC-26</t>
   </si>
   <si>
-    <t>23-DEC-26</t>
-  </si>
-  <si>
-    <t>25-DEC-26</t>
-  </si>
-  <si>
-    <t>27-DEC-26</t>
-  </si>
-  <si>
     <t>28-DEC-26</t>
-  </si>
-  <si>
-    <t>30-DEC-26</t>
   </si>
 </sst>
 </file>
@@ -826,7 +784,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K184"/>
+  <dimension ref="A1:K162"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1024,16 +982,16 @@
         <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2">
-        <v>567</v>
+        <v>427</v>
       </c>
       <c r="E6" s="2">
         <v>531</v>
       </c>
       <c r="F6" s="2">
-        <v>36</v>
+        <v>-104</v>
       </c>
       <c r="G6" s="2">
         <v>46</v>
@@ -1059,7 +1017,7 @@
         <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2">
         <v>567</v>
@@ -1088,10 +1046,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
@@ -1123,31 +1081,31 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2">
-        <v>624</v>
+        <v>534</v>
       </c>
       <c r="E9" s="2">
         <v>500</v>
       </c>
       <c r="F9" s="2">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="G9" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2">
         <v>30</v>
       </c>
       <c r="I9" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>14</v>
@@ -1158,10 +1116,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>23</v>
@@ -1185,7 +1143,7 @@
         <v>-10</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -1193,10 +1151,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>18</v>
@@ -1220,7 +1178,7 @@
         <v>-10</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -1228,10 +1186,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>20</v>
@@ -1255,7 +1213,7 @@
         <v>-10</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -1263,34 +1221,34 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2">
-        <v>439</v>
+        <v>603</v>
       </c>
       <c r="E13" s="2">
         <v>1936</v>
       </c>
       <c r="F13" s="2">
-        <v>-1497</v>
+        <v>-1333</v>
       </c>
       <c r="G13" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2">
         <v>30</v>
       </c>
       <c r="I13" s="2">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -1298,7 +1256,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>22</v>
@@ -1333,7 +1291,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>22</v>
@@ -1368,31 +1326,31 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="E16" s="2">
         <v>500</v>
       </c>
       <c r="F16" s="2">
-        <v>-101</v>
+        <v>-73</v>
       </c>
       <c r="G16" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2">
         <v>30</v>
       </c>
       <c r="I16" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>14</v>
@@ -1403,7 +1361,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1438,7 +1396,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1473,31 +1431,31 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D19" s="2">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="E19" s="2">
         <v>468</v>
       </c>
       <c r="F19" s="2">
-        <v>-69</v>
+        <v>-41</v>
       </c>
       <c r="G19" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2">
         <v>30</v>
       </c>
       <c r="I19" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>14</v>
@@ -1508,7 +1466,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>22</v>
@@ -1543,7 +1501,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>22</v>
@@ -1578,7 +1536,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>22</v>
@@ -1613,7 +1571,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>17</v>
@@ -1648,7 +1606,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>17</v>
@@ -1683,7 +1641,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>17</v>
@@ -1718,13 +1676,13 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D26" s="2">
         <v>399</v>
@@ -1753,7 +1711,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>17</v>
@@ -1788,7 +1746,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>17</v>
@@ -1823,7 +1781,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>22</v>
@@ -1858,7 +1816,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>22</v>
@@ -1893,22 +1851,22 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D31" s="2">
-        <v>427</v>
+        <v>567</v>
       </c>
       <c r="E31" s="2">
         <v>531</v>
       </c>
       <c r="F31" s="2">
-        <v>-104</v>
+        <v>36</v>
       </c>
       <c r="G31" s="2">
         <v>46</v>
@@ -1928,10 +1886,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>20</v>
@@ -1963,7 +1921,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>17</v>
@@ -1998,7 +1956,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>17</v>
@@ -2033,22 +1991,22 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D35" s="2">
-        <v>567</v>
+        <v>427</v>
       </c>
       <c r="E35" s="2">
-        <v>581</v>
+        <v>468</v>
       </c>
       <c r="F35" s="2">
-        <v>-14</v>
+        <v>-41</v>
       </c>
       <c r="G35" s="2">
         <v>46</v>
@@ -2068,13 +2026,13 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D36" s="2">
         <v>567</v>
@@ -2103,31 +2061,31 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D37" s="2">
-        <v>724</v>
+        <v>427</v>
       </c>
       <c r="E37" s="2">
-        <v>581</v>
+        <v>500</v>
       </c>
       <c r="F37" s="2">
-        <v>143</v>
+        <v>-73</v>
       </c>
       <c r="G37" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2">
         <v>30</v>
       </c>
       <c r="I37" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>14</v>
@@ -2138,31 +2096,31 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D38" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="E38" s="2">
         <v>500</v>
       </c>
       <c r="F38" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G38" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2">
         <v>30</v>
       </c>
       <c r="I38" s="2">
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>14</v>
@@ -2173,31 +2131,31 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D39" s="2">
-        <v>529</v>
+        <v>427</v>
       </c>
       <c r="E39" s="2">
         <v>581</v>
       </c>
       <c r="F39" s="2">
-        <v>-52</v>
+        <v>-154</v>
       </c>
       <c r="G39" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2">
         <v>30</v>
       </c>
       <c r="I39" s="2">
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>14</v>
@@ -2208,22 +2166,22 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D40" s="2">
-        <v>427</v>
+        <v>534</v>
       </c>
       <c r="E40" s="2">
-        <v>500</v>
+        <v>581</v>
       </c>
       <c r="F40" s="2">
-        <v>-73</v>
+        <v>-47</v>
       </c>
       <c r="G40" s="2">
         <v>46</v>
@@ -2243,22 +2201,22 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2">
-        <v>534</v>
+        <v>567</v>
       </c>
       <c r="E41" s="2">
-        <v>500</v>
+        <v>581</v>
       </c>
       <c r="F41" s="2">
-        <v>34</v>
+        <v>-14</v>
       </c>
       <c r="G41" s="2">
         <v>46</v>
@@ -2278,22 +2236,22 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D42" s="2">
-        <v>427</v>
+        <v>567</v>
       </c>
       <c r="E42" s="2">
         <v>581</v>
       </c>
       <c r="F42" s="2">
-        <v>-154</v>
+        <v>-14</v>
       </c>
       <c r="G42" s="2">
         <v>46</v>
@@ -2313,22 +2271,22 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D43" s="2">
-        <v>534</v>
+        <v>427</v>
       </c>
       <c r="E43" s="2">
-        <v>581</v>
+        <v>500</v>
       </c>
       <c r="F43" s="2">
-        <v>-47</v>
+        <v>-73</v>
       </c>
       <c r="G43" s="2">
         <v>46</v>
@@ -2348,31 +2306,31 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D44" s="2">
-        <v>724</v>
+        <v>534</v>
       </c>
       <c r="E44" s="2">
-        <v>581</v>
+        <v>500</v>
       </c>
       <c r="F44" s="2">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="G44" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2">
         <v>30</v>
       </c>
       <c r="I44" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>14</v>
@@ -2383,22 +2341,22 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D45" s="2">
-        <v>534</v>
+        <v>427</v>
       </c>
       <c r="E45" s="2">
-        <v>581</v>
+        <v>468</v>
       </c>
       <c r="F45" s="2">
-        <v>-47</v>
+        <v>-41</v>
       </c>
       <c r="G45" s="2">
         <v>46</v>
@@ -2421,19 +2379,19 @@
         <v>48</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D46" s="2">
         <v>427</v>
       </c>
       <c r="E46" s="2">
-        <v>468</v>
+        <v>581</v>
       </c>
       <c r="F46" s="2">
-        <v>-41</v>
+        <v>-154</v>
       </c>
       <c r="G46" s="2">
         <v>46</v>
@@ -2456,19 +2414,19 @@
         <v>49</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D47" s="2">
-        <v>534</v>
+        <v>427</v>
       </c>
       <c r="E47" s="2">
-        <v>581</v>
+        <v>468</v>
       </c>
       <c r="F47" s="2">
-        <v>-47</v>
+        <v>-41</v>
       </c>
       <c r="G47" s="2">
         <v>46</v>
@@ -2488,31 +2446,31 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D48" s="2">
-        <v>529</v>
+        <v>427</v>
       </c>
       <c r="E48" s="2">
         <v>581</v>
       </c>
       <c r="F48" s="2">
-        <v>-52</v>
+        <v>-154</v>
       </c>
       <c r="G48" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2">
         <v>30</v>
       </c>
       <c r="I48" s="2">
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>14</v>
@@ -2523,22 +2481,22 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="D49" s="2">
         <v>427</v>
       </c>
       <c r="E49" s="2">
-        <v>468</v>
+        <v>581</v>
       </c>
       <c r="F49" s="2">
-        <v>-41</v>
+        <v>-154</v>
       </c>
       <c r="G49" s="2">
         <v>46</v>
@@ -2558,31 +2516,31 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D50" s="2">
-        <v>427</v>
+        <v>603</v>
       </c>
       <c r="E50" s="2">
         <v>581</v>
       </c>
       <c r="F50" s="2">
-        <v>-154</v>
+        <v>22</v>
       </c>
       <c r="G50" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H50" s="2">
         <v>30</v>
       </c>
       <c r="I50" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>14</v>
@@ -2593,31 +2551,31 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D51" s="2">
-        <v>529</v>
+        <v>603</v>
       </c>
       <c r="E51" s="2">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="F51" s="2">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="G51" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H51" s="2">
         <v>30</v>
       </c>
       <c r="I51" s="2">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>14</v>
@@ -2628,22 +2586,22 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="D52" s="2">
-        <v>427</v>
+        <v>622</v>
       </c>
       <c r="E52" s="2">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="F52" s="2">
-        <v>-154</v>
+        <v>19</v>
       </c>
       <c r="G52" s="2">
         <v>46</v>
@@ -2663,31 +2621,31 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D53" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="E53" s="2">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="F53" s="2">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G53" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H53" s="2">
         <v>30</v>
       </c>
       <c r="I53" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>14</v>
@@ -2698,22 +2656,22 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D54" s="2">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="E54" s="2">
         <v>603</v>
       </c>
       <c r="F54" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G54" s="2">
         <v>46</v>
@@ -2733,34 +2691,34 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D55" s="2">
-        <v>544</v>
+        <v>309</v>
       </c>
       <c r="E55" s="2">
-        <v>603</v>
+        <v>2109</v>
       </c>
       <c r="F55" s="2">
-        <v>-59</v>
+        <v>-1800</v>
       </c>
       <c r="G55" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H55" s="2">
         <v>30</v>
       </c>
       <c r="I55" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>15</v>
@@ -2768,34 +2726,34 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="D56" s="2">
-        <v>544</v>
+        <v>414</v>
       </c>
       <c r="E56" s="2">
-        <v>603</v>
+        <v>2109</v>
       </c>
       <c r="F56" s="2">
-        <v>-59</v>
+        <v>-1695</v>
       </c>
       <c r="G56" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H56" s="2">
         <v>30</v>
       </c>
       <c r="I56" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>15</v>
@@ -2803,34 +2761,34 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D57" s="2">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="E57" s="2">
-        <v>603</v>
+        <v>2109</v>
       </c>
       <c r="F57" s="2">
-        <v>-59</v>
+        <v>-1690</v>
       </c>
       <c r="G57" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2">
         <v>30</v>
       </c>
       <c r="I57" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>15</v>
@@ -2838,22 +2796,22 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D58" s="2">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="E58" s="2">
-        <v>603</v>
+        <v>2109</v>
       </c>
       <c r="F58" s="2">
-        <v>-59</v>
+        <v>-1575</v>
       </c>
       <c r="G58" s="2">
         <v>40</v>
@@ -2864,8 +2822,8 @@
       <c r="I58" s="2">
         <v>-10</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>14</v>
+      <c r="J58" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>15</v>
@@ -2873,31 +2831,31 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D59" s="2">
-        <v>567</v>
+        <v>603</v>
       </c>
       <c r="E59" s="2">
         <v>603</v>
       </c>
       <c r="F59" s="2">
-        <v>-36</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H59" s="2">
         <v>30</v>
       </c>
       <c r="I59" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>14</v>
@@ -2908,22 +2866,22 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="D60" s="2">
-        <v>622</v>
+        <v>567</v>
       </c>
       <c r="E60" s="2">
         <v>603</v>
       </c>
       <c r="F60" s="2">
-        <v>19</v>
+        <v>-36</v>
       </c>
       <c r="G60" s="2">
         <v>46</v>
@@ -2943,31 +2901,31 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D61" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E61" s="2">
         <v>603</v>
       </c>
       <c r="F61" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G61" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2">
         <v>30</v>
       </c>
       <c r="I61" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>14</v>
@@ -2981,28 +2939,28 @@
         <v>63</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D62" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E62" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F62" s="2">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="G62" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H62" s="2">
         <v>30</v>
       </c>
       <c r="I62" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>14</v>
@@ -3013,34 +2971,34 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D63" s="2">
-        <v>622</v>
+        <v>339</v>
       </c>
       <c r="E63" s="2">
-        <v>603</v>
+        <v>2109</v>
       </c>
       <c r="F63" s="2">
-        <v>19</v>
+        <v>-1770</v>
       </c>
       <c r="G63" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H63" s="2">
         <v>30</v>
       </c>
       <c r="I63" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>15</v>
@@ -3048,34 +3006,34 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="D64" s="2">
-        <v>567</v>
+        <v>414</v>
       </c>
       <c r="E64" s="2">
-        <v>603</v>
+        <v>2109</v>
       </c>
       <c r="F64" s="2">
-        <v>-36</v>
+        <v>-1695</v>
       </c>
       <c r="G64" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H64" s="2">
         <v>30</v>
       </c>
       <c r="I64" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>15</v>
@@ -3083,34 +3041,34 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D65" s="2">
-        <v>632</v>
+        <v>439</v>
       </c>
       <c r="E65" s="2">
-        <v>603</v>
+        <v>2109</v>
       </c>
       <c r="F65" s="2">
-        <v>29</v>
+        <v>-1670</v>
       </c>
       <c r="G65" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H65" s="2">
         <v>30</v>
       </c>
       <c r="I65" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>15</v>
@@ -3118,22 +3076,22 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D66" s="2">
-        <v>624</v>
+        <v>574</v>
       </c>
       <c r="E66" s="2">
-        <v>478</v>
+        <v>2109</v>
       </c>
       <c r="F66" s="2">
-        <v>146</v>
+        <v>-1535</v>
       </c>
       <c r="G66" s="2">
         <v>40</v>
@@ -3144,8 +3102,8 @@
       <c r="I66" s="2">
         <v>-10</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>14</v>
+      <c r="J66" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>15</v>
@@ -3153,34 +3111,34 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D67" s="2">
-        <v>414</v>
+        <v>567</v>
       </c>
       <c r="E67" s="2">
-        <v>2109</v>
+        <v>603</v>
       </c>
       <c r="F67" s="2">
-        <v>-1695</v>
+        <v>-36</v>
       </c>
       <c r="G67" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H67" s="2">
         <v>30</v>
       </c>
       <c r="I67" s="2">
-        <v>0</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>30</v>
+        <v>-16</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>15</v>
@@ -3191,31 +3149,31 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D68" s="2">
-        <v>544</v>
+        <v>632</v>
       </c>
       <c r="E68" s="2">
-        <v>2109</v>
+        <v>603</v>
       </c>
       <c r="F68" s="2">
-        <v>-1565</v>
+        <v>29</v>
       </c>
       <c r="G68" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2">
         <v>30</v>
       </c>
       <c r="I68" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>30</v>
+        <v>-16</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>15</v>
@@ -3223,34 +3181,34 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="D69" s="2">
-        <v>544</v>
+        <v>439</v>
       </c>
       <c r="E69" s="2">
-        <v>2109</v>
+        <v>933</v>
       </c>
       <c r="F69" s="2">
-        <v>-1565</v>
+        <v>-494</v>
       </c>
       <c r="G69" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2">
         <v>30</v>
       </c>
       <c r="I69" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>30</v>
+        <v>30</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>15</v>
@@ -3258,34 +3216,34 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D70" s="2">
-        <v>624</v>
+        <v>479</v>
       </c>
       <c r="E70" s="2">
-        <v>2109</v>
+        <v>933</v>
       </c>
       <c r="F70" s="2">
-        <v>-1485</v>
+        <v>-454</v>
       </c>
       <c r="G70" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H70" s="2">
         <v>30</v>
       </c>
       <c r="I70" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>15</v>
@@ -3293,34 +3251,34 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="2">
+        <v>479</v>
+      </c>
+      <c r="E71" s="2">
+        <v>933</v>
+      </c>
+      <c r="F71" s="2">
+        <v>-454</v>
+      </c>
+      <c r="G71" s="2">
+        <v>30</v>
+      </c>
+      <c r="H71" s="2">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+      <c r="J71" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D71" s="2">
-        <v>622</v>
-      </c>
-      <c r="E71" s="2">
-        <v>603</v>
-      </c>
-      <c r="F71" s="2">
-        <v>19</v>
-      </c>
-      <c r="G71" s="2">
-        <v>46</v>
-      </c>
-      <c r="H71" s="2">
-        <v>30</v>
-      </c>
-      <c r="I71" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>15</v>
@@ -3328,34 +3286,34 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D72" s="2">
-        <v>567</v>
+        <v>644</v>
       </c>
       <c r="E72" s="2">
-        <v>603</v>
+        <v>933</v>
       </c>
       <c r="F72" s="2">
-        <v>-36</v>
+        <v>-289</v>
       </c>
       <c r="G72" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H72" s="2">
         <v>30</v>
       </c>
       <c r="I72" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>14</v>
+        <v>-10</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>15</v>
@@ -3366,28 +3324,28 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D73" s="2">
-        <v>622</v>
+        <v>309</v>
       </c>
       <c r="E73" s="2">
-        <v>603</v>
+        <v>933</v>
       </c>
       <c r="F73" s="2">
-        <v>19</v>
+        <v>-624</v>
       </c>
       <c r="G73" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H73" s="2">
         <v>30</v>
       </c>
       <c r="I73" s="2">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>14</v>
@@ -3398,22 +3356,22 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D74" s="2">
-        <v>339</v>
+        <v>309</v>
       </c>
       <c r="E74" s="2">
-        <v>2109</v>
+        <v>933</v>
       </c>
       <c r="F74" s="2">
-        <v>-1770</v>
+        <v>-624</v>
       </c>
       <c r="G74" s="2">
         <v>15</v>
@@ -3424,8 +3382,8 @@
       <c r="I74" s="2">
         <v>15</v>
       </c>
-      <c r="J74" s="4" t="s">
-        <v>30</v>
+      <c r="J74" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>15</v>
@@ -3433,34 +3391,34 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D75" s="2">
-        <v>339</v>
+        <v>414</v>
       </c>
       <c r="E75" s="2">
-        <v>2109</v>
+        <v>933</v>
       </c>
       <c r="F75" s="2">
-        <v>-1770</v>
+        <v>-519</v>
       </c>
       <c r="G75" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H75" s="2">
         <v>30</v>
       </c>
       <c r="I75" s="2">
-        <v>15</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>15</v>
@@ -3468,34 +3426,34 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D76" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E76" s="2">
-        <v>2109</v>
+        <v>933</v>
       </c>
       <c r="F76" s="2">
-        <v>-1695</v>
+        <v>-514</v>
       </c>
       <c r="G76" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H76" s="2">
         <v>30</v>
       </c>
       <c r="I76" s="2">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>30</v>
+        <v>30</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>15</v>
@@ -3506,31 +3464,31 @@
         <v>74</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D77" s="2">
-        <v>439</v>
+        <v>624</v>
       </c>
       <c r="E77" s="2">
-        <v>2109</v>
+        <v>478</v>
       </c>
       <c r="F77" s="2">
-        <v>-1670</v>
+        <v>146</v>
       </c>
       <c r="G77" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H77" s="2">
         <v>30</v>
       </c>
       <c r="I77" s="2">
-        <v>30</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>30</v>
+        <v>-10</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>15</v>
@@ -3538,22 +3496,22 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="D78" s="2">
-        <v>622</v>
+        <v>427</v>
       </c>
       <c r="E78" s="2">
         <v>603</v>
       </c>
       <c r="F78" s="2">
-        <v>19</v>
+        <v>-176</v>
       </c>
       <c r="G78" s="2">
         <v>46</v>
@@ -3564,8 +3522,8 @@
       <c r="I78" s="2">
         <v>-16</v>
       </c>
-      <c r="J78" s="3" t="s">
-        <v>14</v>
+      <c r="J78" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>15</v>
@@ -3573,22 +3531,22 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="D79" s="2">
-        <v>567</v>
+        <v>427</v>
       </c>
       <c r="E79" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F79" s="2">
-        <v>-36</v>
+        <v>-51</v>
       </c>
       <c r="G79" s="2">
         <v>46</v>
@@ -3608,22 +3566,22 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D80" s="2">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="E80" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F80" s="2">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="G80" s="2">
         <v>40</v>
@@ -3643,22 +3601,22 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D81" s="2">
-        <v>632</v>
+        <v>427</v>
       </c>
       <c r="E81" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F81" s="2">
-        <v>29</v>
+        <v>-51</v>
       </c>
       <c r="G81" s="2">
         <v>46</v>
@@ -3678,31 +3636,31 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D82" s="2">
-        <v>309</v>
+        <v>534</v>
       </c>
       <c r="E82" s="2">
-        <v>933</v>
+        <v>603</v>
       </c>
       <c r="F82" s="2">
-        <v>-624</v>
+        <v>-69</v>
       </c>
       <c r="G82" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H82" s="2">
         <v>30</v>
       </c>
       <c r="I82" s="2">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>14</v>
@@ -3713,31 +3671,31 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D83" s="2">
-        <v>309</v>
+        <v>427</v>
       </c>
       <c r="E83" s="2">
-        <v>933</v>
+        <v>478</v>
       </c>
       <c r="F83" s="2">
-        <v>-624</v>
+        <v>-51</v>
       </c>
       <c r="G83" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H83" s="2">
         <v>30</v>
       </c>
       <c r="I83" s="2">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>14</v>
@@ -3748,34 +3706,34 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D84" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="E84" s="2">
-        <v>933</v>
+        <v>603</v>
       </c>
       <c r="F84" s="2">
-        <v>-519</v>
+        <v>-176</v>
       </c>
       <c r="G84" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H84" s="2">
         <v>30</v>
       </c>
       <c r="I84" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>15</v>
@@ -3783,31 +3741,31 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D85" s="2">
-        <v>439</v>
+        <v>622</v>
       </c>
       <c r="E85" s="2">
-        <v>933</v>
+        <v>603</v>
       </c>
       <c r="F85" s="2">
-        <v>-494</v>
+        <v>19</v>
       </c>
       <c r="G85" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H85" s="2">
         <v>30</v>
       </c>
       <c r="I85" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>14</v>
@@ -3818,34 +3776,34 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D86" s="2">
-        <v>414</v>
+        <v>622</v>
       </c>
       <c r="E86" s="2">
-        <v>933</v>
+        <v>603</v>
       </c>
       <c r="F86" s="2">
-        <v>-519</v>
+        <v>19</v>
       </c>
       <c r="G86" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H86" s="2">
         <v>30</v>
       </c>
       <c r="I86" s="2">
-        <v>0</v>
-      </c>
-      <c r="J86" s="5" t="s">
-        <v>82</v>
+        <v>-16</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>15</v>
@@ -3853,31 +3811,31 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D87" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="E87" s="2">
-        <v>933</v>
+        <v>478</v>
       </c>
       <c r="F87" s="2">
-        <v>-514</v>
+        <v>-51</v>
       </c>
       <c r="G87" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H87" s="2">
         <v>30</v>
       </c>
       <c r="I87" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J87" s="3" t="s">
         <v>14</v>
@@ -3891,31 +3849,31 @@
         <v>83</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="D88" s="2">
-        <v>479</v>
+        <v>603</v>
       </c>
       <c r="E88" s="2">
-        <v>933</v>
+        <v>478</v>
       </c>
       <c r="F88" s="2">
-        <v>-454</v>
+        <v>125</v>
       </c>
       <c r="G88" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H88" s="2">
         <v>30</v>
       </c>
       <c r="I88" s="2">
-        <v>0</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>82</v>
+        <v>-10</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>15</v>
@@ -3923,34 +3881,34 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D89" s="2">
-        <v>622</v>
+        <v>534</v>
       </c>
       <c r="E89" s="2">
-        <v>933</v>
+        <v>603</v>
       </c>
       <c r="F89" s="2">
-        <v>-311</v>
+        <v>-69</v>
       </c>
       <c r="G89" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H89" s="2">
         <v>30</v>
       </c>
       <c r="I89" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J89" s="5" t="s">
-        <v>82</v>
+        <v>-10</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>15</v>
@@ -3961,19 +3919,19 @@
         <v>84</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D90" s="2">
-        <v>624</v>
+        <v>534</v>
       </c>
       <c r="E90" s="2">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="F90" s="2">
-        <v>146</v>
+        <v>-69</v>
       </c>
       <c r="G90" s="2">
         <v>40</v>
@@ -3993,31 +3951,31 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D91" s="2">
-        <v>622</v>
+        <v>534</v>
       </c>
       <c r="E91" s="2">
         <v>603</v>
       </c>
       <c r="F91" s="2">
-        <v>19</v>
+        <v>-69</v>
       </c>
       <c r="G91" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H91" s="2">
         <v>30</v>
       </c>
       <c r="I91" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>14</v>
@@ -4034,25 +3992,25 @@
         <v>22</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D92" s="2">
-        <v>624</v>
+        <v>427</v>
       </c>
       <c r="E92" s="2">
         <v>478</v>
       </c>
       <c r="F92" s="2">
-        <v>146</v>
+        <v>-51</v>
       </c>
       <c r="G92" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H92" s="2">
         <v>30</v>
       </c>
       <c r="I92" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>14</v>
@@ -4063,31 +4021,31 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D93" s="2">
-        <v>624</v>
+        <v>427</v>
       </c>
       <c r="E93" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F93" s="2">
-        <v>21</v>
+        <v>-51</v>
       </c>
       <c r="G93" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H93" s="2">
         <v>30</v>
       </c>
       <c r="I93" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J93" s="3" t="s">
         <v>14</v>
@@ -4101,19 +4059,19 @@
         <v>87</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D94" s="2">
         <v>427</v>
       </c>
       <c r="E94" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F94" s="2">
-        <v>-176</v>
+        <v>-51</v>
       </c>
       <c r="G94" s="2">
         <v>46</v>
@@ -4124,8 +4082,8 @@
       <c r="I94" s="2">
         <v>-16</v>
       </c>
-      <c r="J94" s="5" t="s">
-        <v>82</v>
+      <c r="J94" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>15</v>
@@ -4133,31 +4091,31 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D95" s="2">
-        <v>427</v>
+        <v>603</v>
       </c>
       <c r="E95" s="2">
         <v>478</v>
       </c>
       <c r="F95" s="2">
-        <v>-51</v>
+        <v>125</v>
       </c>
       <c r="G95" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H95" s="2">
         <v>30</v>
       </c>
       <c r="I95" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J95" s="3" t="s">
         <v>14</v>
@@ -4171,19 +4129,19 @@
         <v>88</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D96" s="2">
-        <v>624</v>
+        <v>534</v>
       </c>
       <c r="E96" s="2">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="F96" s="2">
-        <v>146</v>
+        <v>-69</v>
       </c>
       <c r="G96" s="2">
         <v>40</v>
@@ -4203,31 +4161,31 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="D97" s="2">
-        <v>427</v>
+        <v>534</v>
       </c>
       <c r="E97" s="2">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="F97" s="2">
-        <v>-51</v>
+        <v>-69</v>
       </c>
       <c r="G97" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H97" s="2">
         <v>30</v>
       </c>
       <c r="I97" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J97" s="3" t="s">
         <v>14</v>
@@ -4238,22 +4196,22 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D98" s="2">
-        <v>427</v>
+        <v>567</v>
       </c>
       <c r="E98" s="2">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="F98" s="2">
-        <v>-51</v>
+        <v>-36</v>
       </c>
       <c r="G98" s="2">
         <v>46</v>
@@ -4273,22 +4231,22 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D99" s="2">
-        <v>624</v>
+        <v>534</v>
       </c>
       <c r="E99" s="2">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="F99" s="2">
-        <v>146</v>
+        <v>-69</v>
       </c>
       <c r="G99" s="2">
         <v>40</v>
@@ -4308,22 +4266,22 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="D100" s="2">
-        <v>427</v>
+        <v>622</v>
       </c>
       <c r="E100" s="2">
         <v>603</v>
       </c>
       <c r="F100" s="2">
-        <v>-176</v>
+        <v>19</v>
       </c>
       <c r="G100" s="2">
         <v>46</v>
@@ -4334,8 +4292,8 @@
       <c r="I100" s="2">
         <v>-16</v>
       </c>
-      <c r="J100" s="5" t="s">
-        <v>82</v>
+      <c r="J100" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>15</v>
@@ -4343,31 +4301,31 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D101" s="2">
-        <v>624</v>
+        <v>567</v>
       </c>
       <c r="E101" s="2">
         <v>603</v>
       </c>
       <c r="F101" s="2">
-        <v>21</v>
+        <v>-36</v>
       </c>
       <c r="G101" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H101" s="2">
         <v>30</v>
       </c>
       <c r="I101" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>14</v>
@@ -4378,22 +4336,22 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="D102" s="2">
-        <v>427</v>
+        <v>622</v>
       </c>
       <c r="E102" s="2">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="F102" s="2">
-        <v>-51</v>
+        <v>19</v>
       </c>
       <c r="G102" s="2">
         <v>46</v>
@@ -4413,31 +4371,31 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D103" s="2">
-        <v>624</v>
+        <v>427</v>
       </c>
       <c r="E103" s="2">
         <v>478</v>
       </c>
       <c r="F103" s="2">
-        <v>146</v>
+        <v>-51</v>
       </c>
       <c r="G103" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H103" s="2">
         <v>30</v>
       </c>
       <c r="I103" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J103" s="3" t="s">
         <v>14</v>
@@ -4448,31 +4406,31 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D104" s="2">
-        <v>534</v>
+        <v>603</v>
       </c>
       <c r="E104" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F104" s="2">
-        <v>-69</v>
+        <v>125</v>
       </c>
       <c r="G104" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H104" s="2">
         <v>30</v>
       </c>
       <c r="I104" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>14</v>
@@ -4483,31 +4441,31 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D105" s="2">
-        <v>624</v>
+        <v>427</v>
       </c>
       <c r="E105" s="2">
         <v>478</v>
       </c>
       <c r="F105" s="2">
-        <v>146</v>
+        <v>-51</v>
       </c>
       <c r="G105" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H105" s="2">
         <v>30</v>
       </c>
       <c r="I105" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J105" s="3" t="s">
         <v>14</v>
@@ -4518,31 +4476,31 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D106" s="2">
-        <v>622</v>
+        <v>603</v>
       </c>
       <c r="E106" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F106" s="2">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="G106" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H106" s="2">
         <v>30</v>
       </c>
       <c r="I106" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J106" s="3" t="s">
         <v>14</v>
@@ -4553,31 +4511,31 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D107" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E107" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F107" s="2">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="G107" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H107" s="2">
         <v>30</v>
       </c>
       <c r="I107" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J107" s="3" t="s">
         <v>14</v>
@@ -4588,31 +4546,31 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D108" s="2">
-        <v>622</v>
+        <v>413</v>
       </c>
       <c r="E108" s="2">
-        <v>603</v>
+        <v>858</v>
       </c>
       <c r="F108" s="2">
-        <v>19</v>
+        <v>-445</v>
       </c>
       <c r="G108" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H108" s="2">
         <v>30</v>
       </c>
       <c r="I108" s="2">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J108" s="3" t="s">
         <v>14</v>
@@ -4623,31 +4581,31 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="D109" s="2">
-        <v>427</v>
+        <v>549</v>
       </c>
       <c r="E109" s="2">
-        <v>478</v>
+        <v>858</v>
       </c>
       <c r="F109" s="2">
-        <v>-51</v>
+        <v>-309</v>
       </c>
       <c r="G109" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H109" s="2">
         <v>30</v>
       </c>
       <c r="I109" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J109" s="3" t="s">
         <v>14</v>
@@ -4658,22 +4616,22 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="C110" s="2" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D110" s="2">
-        <v>427</v>
+        <v>619</v>
       </c>
       <c r="E110" s="2">
-        <v>478</v>
+        <v>858</v>
       </c>
       <c r="F110" s="2">
-        <v>-51</v>
+        <v>-239</v>
       </c>
       <c r="G110" s="2">
         <v>46</v>
@@ -4684,8 +4642,8 @@
       <c r="I110" s="2">
         <v>-16</v>
       </c>
-      <c r="J110" s="3" t="s">
-        <v>14</v>
+      <c r="J110" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>15</v>
@@ -4693,31 +4651,31 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D111" s="2">
-        <v>427</v>
+        <v>549</v>
       </c>
       <c r="E111" s="2">
-        <v>478</v>
+        <v>858</v>
       </c>
       <c r="F111" s="2">
-        <v>-51</v>
+        <v>-309</v>
       </c>
       <c r="G111" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H111" s="2">
         <v>30</v>
       </c>
       <c r="I111" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J111" s="3" t="s">
         <v>14</v>
@@ -4728,31 +4686,31 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D112" s="2">
-        <v>427</v>
+        <v>638</v>
       </c>
       <c r="E112" s="2">
-        <v>478</v>
+        <v>858</v>
       </c>
       <c r="F112" s="2">
-        <v>-51</v>
+        <v>-220</v>
       </c>
       <c r="G112" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H112" s="2">
         <v>30</v>
       </c>
       <c r="I112" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J112" s="3" t="s">
         <v>14</v>
@@ -4763,31 +4721,31 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D113" s="2">
-        <v>624</v>
+        <v>719</v>
       </c>
       <c r="E113" s="2">
-        <v>478</v>
+        <v>858</v>
       </c>
       <c r="F113" s="2">
-        <v>146</v>
+        <v>-139</v>
       </c>
       <c r="G113" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H113" s="2">
         <v>30</v>
       </c>
       <c r="I113" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J113" s="3" t="s">
         <v>14</v>
@@ -4798,31 +4756,31 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D114" s="2">
-        <v>567</v>
+        <v>624</v>
       </c>
       <c r="E114" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F114" s="2">
-        <v>-36</v>
+        <v>146</v>
       </c>
       <c r="G114" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H114" s="2">
         <v>30</v>
       </c>
       <c r="I114" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J114" s="3" t="s">
         <v>14</v>
@@ -4833,31 +4791,31 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D115" s="2">
-        <v>567</v>
+        <v>624</v>
       </c>
       <c r="E115" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F115" s="2">
-        <v>-36</v>
+        <v>146</v>
       </c>
       <c r="G115" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H115" s="2">
         <v>30</v>
       </c>
       <c r="I115" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J115" s="3" t="s">
         <v>14</v>
@@ -4868,31 +4826,31 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="D116" s="2">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="E116" s="2">
-        <v>478</v>
+        <v>858</v>
       </c>
       <c r="F116" s="2">
-        <v>-51</v>
+        <v>-445</v>
       </c>
       <c r="G116" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H116" s="2">
         <v>30</v>
       </c>
       <c r="I116" s="2">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J116" s="3" t="s">
         <v>14</v>
@@ -4903,31 +4861,31 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D117" s="2">
-        <v>624</v>
+        <v>413</v>
       </c>
       <c r="E117" s="2">
-        <v>478</v>
+        <v>858</v>
       </c>
       <c r="F117" s="2">
-        <v>146</v>
+        <v>-445</v>
       </c>
       <c r="G117" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H117" s="2">
         <v>30</v>
       </c>
       <c r="I117" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J117" s="3" t="s">
         <v>14</v>
@@ -4941,28 +4899,28 @@
         <v>104</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="D118" s="2">
-        <v>624</v>
+        <v>549</v>
       </c>
       <c r="E118" s="2">
-        <v>478</v>
+        <v>858</v>
       </c>
       <c r="F118" s="2">
-        <v>146</v>
+        <v>-309</v>
       </c>
       <c r="G118" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H118" s="2">
         <v>30</v>
       </c>
       <c r="I118" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J118" s="3" t="s">
         <v>14</v>
@@ -4976,19 +4934,19 @@
         <v>105</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D119" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E119" s="2">
         <v>858</v>
       </c>
       <c r="F119" s="2">
-        <v>-443</v>
+        <v>-445</v>
       </c>
       <c r="G119" s="2">
         <v>20</v>
@@ -5011,28 +4969,28 @@
         <v>105</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D120" s="2">
-        <v>549</v>
+        <v>519</v>
       </c>
       <c r="E120" s="2">
         <v>858</v>
       </c>
       <c r="F120" s="2">
-        <v>-309</v>
+        <v>-339</v>
       </c>
       <c r="G120" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H120" s="2">
         <v>30</v>
       </c>
       <c r="I120" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J120" s="3" t="s">
         <v>14</v>
@@ -5046,31 +5004,31 @@
         <v>105</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D121" s="2">
-        <v>619</v>
+        <v>549</v>
       </c>
       <c r="E121" s="2">
         <v>858</v>
       </c>
       <c r="F121" s="2">
-        <v>-239</v>
+        <v>-309</v>
       </c>
       <c r="G121" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H121" s="2">
         <v>30</v>
       </c>
       <c r="I121" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J121" s="5" t="s">
-        <v>82</v>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>15</v>
@@ -5078,31 +5036,31 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="D122" s="2">
-        <v>624</v>
+        <v>413</v>
       </c>
       <c r="E122" s="2">
-        <v>478</v>
+        <v>783</v>
       </c>
       <c r="F122" s="2">
-        <v>146</v>
+        <v>-370</v>
       </c>
       <c r="G122" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H122" s="2">
         <v>30</v>
       </c>
       <c r="I122" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J122" s="3" t="s">
         <v>14</v>
@@ -5113,22 +5071,22 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D123" s="2">
         <v>549</v>
       </c>
       <c r="E123" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F123" s="2">
-        <v>-309</v>
+        <v>-234</v>
       </c>
       <c r="G123" s="2">
         <v>30</v>
@@ -5148,22 +5106,22 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D124" s="2">
-        <v>622</v>
+        <v>534</v>
       </c>
       <c r="E124" s="2">
         <v>858</v>
       </c>
       <c r="F124" s="2">
-        <v>-236</v>
+        <v>-324</v>
       </c>
       <c r="G124" s="2">
         <v>46</v>
@@ -5175,7 +5133,7 @@
         <v>-16</v>
       </c>
       <c r="J124" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>15</v>
@@ -5183,22 +5141,22 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D125" s="2">
-        <v>719</v>
+        <v>569</v>
       </c>
       <c r="E125" s="2">
         <v>858</v>
       </c>
       <c r="F125" s="2">
-        <v>-139</v>
+        <v>-289</v>
       </c>
       <c r="G125" s="2">
         <v>46</v>
@@ -5209,8 +5167,8 @@
       <c r="I125" s="2">
         <v>-16</v>
       </c>
-      <c r="J125" s="3" t="s">
-        <v>14</v>
+      <c r="J125" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>15</v>
@@ -5218,34 +5176,34 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D126" s="2">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="E126" s="2">
-        <v>478</v>
+        <v>858</v>
       </c>
       <c r="F126" s="2">
-        <v>146</v>
+        <v>-239</v>
       </c>
       <c r="G126" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H126" s="2">
         <v>30</v>
       </c>
       <c r="I126" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J126" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J126" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>15</v>
@@ -5253,34 +5211,34 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D127" s="2">
-        <v>624</v>
+        <v>534</v>
       </c>
       <c r="E127" s="2">
-        <v>478</v>
+        <v>783</v>
       </c>
       <c r="F127" s="2">
-        <v>146</v>
+        <v>-249</v>
       </c>
       <c r="G127" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H127" s="2">
         <v>30</v>
       </c>
       <c r="I127" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J127" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J127" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>15</v>
@@ -5288,34 +5246,34 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="D128" s="2">
-        <v>415</v>
+        <v>569</v>
       </c>
       <c r="E128" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F128" s="2">
-        <v>-443</v>
+        <v>-214</v>
       </c>
       <c r="G128" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H128" s="2">
         <v>30</v>
       </c>
       <c r="I128" s="2">
-        <v>10</v>
-      </c>
-      <c r="J128" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J128" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>15</v>
@@ -5323,34 +5281,34 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D129" s="2">
-        <v>549</v>
+        <v>619</v>
       </c>
       <c r="E129" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F129" s="2">
-        <v>-309</v>
+        <v>-164</v>
       </c>
       <c r="G129" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H129" s="2">
         <v>30</v>
       </c>
       <c r="I129" s="2">
-        <v>0</v>
-      </c>
-      <c r="J129" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J129" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>15</v>
@@ -5358,22 +5316,22 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D130" s="2">
-        <v>622</v>
+        <v>534</v>
       </c>
       <c r="E130" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F130" s="2">
-        <v>-236</v>
+        <v>-249</v>
       </c>
       <c r="G130" s="2">
         <v>46</v>
@@ -5385,7 +5343,7 @@
         <v>-16</v>
       </c>
       <c r="J130" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>15</v>
@@ -5393,34 +5351,34 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="D131" s="2">
-        <v>415</v>
+        <v>569</v>
       </c>
       <c r="E131" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F131" s="2">
-        <v>-443</v>
+        <v>-214</v>
       </c>
       <c r="G131" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H131" s="2">
         <v>30</v>
       </c>
       <c r="I131" s="2">
-        <v>10</v>
-      </c>
-      <c r="J131" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J131" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>15</v>
@@ -5428,34 +5386,34 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D132" s="2">
-        <v>519</v>
+        <v>619</v>
       </c>
       <c r="E132" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F132" s="2">
-        <v>-339</v>
+        <v>-164</v>
       </c>
       <c r="G132" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H132" s="2">
         <v>30</v>
       </c>
       <c r="I132" s="2">
-        <v>7</v>
-      </c>
-      <c r="J132" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J132" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>15</v>
@@ -5463,34 +5421,34 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D133" s="2">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="E133" s="2">
         <v>858</v>
       </c>
       <c r="F133" s="2">
-        <v>-309</v>
+        <v>-324</v>
       </c>
       <c r="G133" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H133" s="2">
         <v>30</v>
       </c>
       <c r="I133" s="2">
-        <v>0</v>
-      </c>
-      <c r="J133" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J133" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>15</v>
@@ -5498,34 +5456,34 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="D134" s="2">
-        <v>415</v>
+        <v>619</v>
       </c>
       <c r="E134" s="2">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="F134" s="2">
-        <v>-368</v>
+        <v>-239</v>
       </c>
       <c r="G134" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H134" s="2">
         <v>30</v>
       </c>
       <c r="I134" s="2">
-        <v>10</v>
-      </c>
-      <c r="J134" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J134" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>15</v>
@@ -5533,31 +5491,31 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D135" s="2">
-        <v>549</v>
+        <v>719</v>
       </c>
       <c r="E135" s="2">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="F135" s="2">
-        <v>-234</v>
+        <v>-139</v>
       </c>
       <c r="G135" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H135" s="2">
         <v>30</v>
       </c>
       <c r="I135" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J135" s="3" t="s">
         <v>14</v>
@@ -5568,10 +5526,10 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>24</v>
@@ -5580,10 +5538,10 @@
         <v>534</v>
       </c>
       <c r="E136" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F136" s="2">
-        <v>-324</v>
+        <v>-249</v>
       </c>
       <c r="G136" s="2">
         <v>46</v>
@@ -5595,7 +5553,7 @@
         <v>-16</v>
       </c>
       <c r="J136" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>15</v>
@@ -5603,22 +5561,22 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D137" s="2">
-        <v>569</v>
+        <v>619</v>
       </c>
       <c r="E137" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F137" s="2">
-        <v>-289</v>
+        <v>-164</v>
       </c>
       <c r="G137" s="2">
         <v>46</v>
@@ -5630,7 +5588,7 @@
         <v>-16</v>
       </c>
       <c r="J137" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>15</v>
@@ -5638,22 +5596,22 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D138" s="2">
-        <v>619</v>
+        <v>719</v>
       </c>
       <c r="E138" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F138" s="2">
-        <v>-239</v>
+        <v>-64</v>
       </c>
       <c r="G138" s="2">
         <v>46</v>
@@ -5664,8 +5622,8 @@
       <c r="I138" s="2">
         <v>-16</v>
       </c>
-      <c r="J138" s="5" t="s">
-        <v>82</v>
+      <c r="J138" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K138" s="2" t="s">
         <v>15</v>
@@ -5673,34 +5631,34 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D139" s="2">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="E139" s="2">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="F139" s="2">
-        <v>-249</v>
+        <v>-339</v>
       </c>
       <c r="G139" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H139" s="2">
         <v>30</v>
       </c>
       <c r="I139" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J139" s="5" t="s">
-        <v>82</v>
+        <v>7</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>15</v>
@@ -5708,34 +5666,34 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D140" s="2">
-        <v>569</v>
+        <v>549</v>
       </c>
       <c r="E140" s="2">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="F140" s="2">
-        <v>-214</v>
+        <v>-309</v>
       </c>
       <c r="G140" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H140" s="2">
         <v>30</v>
       </c>
       <c r="I140" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J140" s="5" t="s">
-        <v>82</v>
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K140" s="2" t="s">
         <v>15</v>
@@ -5743,22 +5701,22 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D141" s="2">
         <v>619</v>
       </c>
       <c r="E141" s="2">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="F141" s="2">
-        <v>-164</v>
+        <v>-239</v>
       </c>
       <c r="G141" s="2">
         <v>46</v>
@@ -5770,7 +5728,7 @@
         <v>-16</v>
       </c>
       <c r="J141" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>15</v>
@@ -5778,34 +5736,34 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D142" s="2">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="E142" s="2">
         <v>783</v>
       </c>
       <c r="F142" s="2">
-        <v>-249</v>
+        <v>-234</v>
       </c>
       <c r="G142" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H142" s="2">
         <v>30</v>
       </c>
       <c r="I142" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J142" s="5" t="s">
-        <v>82</v>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>15</v>
@@ -5813,22 +5771,22 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D143" s="2">
-        <v>569</v>
+        <v>619</v>
       </c>
       <c r="E143" s="2">
         <v>783</v>
       </c>
       <c r="F143" s="2">
-        <v>-214</v>
+        <v>-164</v>
       </c>
       <c r="G143" s="2">
         <v>46</v>
@@ -5840,7 +5798,7 @@
         <v>-16</v>
       </c>
       <c r="J143" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>15</v>
@@ -5848,34 +5806,34 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D144" s="2">
-        <v>619</v>
+        <v>413</v>
       </c>
       <c r="E144" s="2">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="F144" s="2">
-        <v>-164</v>
+        <v>-445</v>
       </c>
       <c r="G144" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H144" s="2">
         <v>30</v>
       </c>
       <c r="I144" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J144" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>15</v>
@@ -5883,34 +5841,34 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D145" s="2">
-        <v>624</v>
+        <v>413</v>
       </c>
       <c r="E145" s="2">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="F145" s="2">
-        <v>-159</v>
+        <v>-445</v>
       </c>
       <c r="G145" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H145" s="2">
         <v>30</v>
       </c>
       <c r="I145" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J145" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K145" s="2" t="s">
         <v>15</v>
@@ -5918,34 +5876,34 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D146" s="2">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="E146" s="2">
         <v>858</v>
       </c>
       <c r="F146" s="2">
-        <v>-324</v>
+        <v>-309</v>
       </c>
       <c r="G146" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H146" s="2">
         <v>30</v>
       </c>
       <c r="I146" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J146" s="5" t="s">
-        <v>82</v>
+        <v>0</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K146" s="2" t="s">
         <v>15</v>
@@ -5953,34 +5911,34 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D147" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="E147" s="2">
-        <v>858</v>
+        <v>478</v>
       </c>
       <c r="F147" s="2">
-        <v>-239</v>
+        <v>146</v>
       </c>
       <c r="G147" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H147" s="2">
         <v>30</v>
       </c>
       <c r="I147" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J147" s="5" t="s">
-        <v>82</v>
+        <v>-10</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K147" s="2" t="s">
         <v>15</v>
@@ -5988,22 +5946,22 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D148" s="2">
-        <v>719</v>
+        <v>534</v>
       </c>
       <c r="E148" s="2">
         <v>858</v>
       </c>
       <c r="F148" s="2">
-        <v>-139</v>
+        <v>-324</v>
       </c>
       <c r="G148" s="2">
         <v>46</v>
@@ -6014,8 +5972,8 @@
       <c r="I148" s="2">
         <v>-16</v>
       </c>
-      <c r="J148" s="3" t="s">
-        <v>14</v>
+      <c r="J148" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="K148" s="2" t="s">
         <v>15</v>
@@ -6023,34 +5981,34 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D149" s="2">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="E149" s="2">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="F149" s="2">
-        <v>-249</v>
+        <v>-309</v>
       </c>
       <c r="G149" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H149" s="2">
         <v>30</v>
       </c>
       <c r="I149" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J149" s="5" t="s">
-        <v>82</v>
+        <v>0</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K149" s="2" t="s">
         <v>15</v>
@@ -6058,22 +6016,22 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D150" s="2">
-        <v>619</v>
+        <v>569</v>
       </c>
       <c r="E150" s="2">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="F150" s="2">
-        <v>-164</v>
+        <v>-289</v>
       </c>
       <c r="G150" s="2">
         <v>46</v>
@@ -6085,7 +6043,7 @@
         <v>-16</v>
       </c>
       <c r="J150" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K150" s="2" t="s">
         <v>15</v>
@@ -6093,31 +6051,31 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D151" s="2">
-        <v>719</v>
+        <v>413</v>
       </c>
       <c r="E151" s="2">
         <v>783</v>
       </c>
       <c r="F151" s="2">
-        <v>-64</v>
+        <v>-370</v>
       </c>
       <c r="G151" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H151" s="2">
         <v>30</v>
       </c>
       <c r="I151" s="2">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J151" s="3" t="s">
         <v>14</v>
@@ -6128,31 +6086,31 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="D152" s="2">
-        <v>519</v>
+        <v>413</v>
       </c>
       <c r="E152" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F152" s="2">
-        <v>-339</v>
+        <v>-370</v>
       </c>
       <c r="G152" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H152" s="2">
         <v>30</v>
       </c>
       <c r="I152" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J152" s="3" t="s">
         <v>14</v>
@@ -6163,22 +6121,22 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D153" s="2">
         <v>549</v>
       </c>
       <c r="E153" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F153" s="2">
-        <v>-309</v>
+        <v>-234</v>
       </c>
       <c r="G153" s="2">
         <v>30</v>
@@ -6198,34 +6156,34 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D154" s="2">
-        <v>619</v>
+        <v>413</v>
       </c>
       <c r="E154" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F154" s="2">
-        <v>-239</v>
+        <v>-370</v>
       </c>
       <c r="G154" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H154" s="2">
         <v>30</v>
       </c>
       <c r="I154" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J154" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
+      </c>
+      <c r="J154" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K154" s="2" t="s">
         <v>15</v>
@@ -6233,34 +6191,34 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D155" s="2">
-        <v>624</v>
+        <v>413</v>
       </c>
       <c r="E155" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F155" s="2">
-        <v>-234</v>
+        <v>-370</v>
       </c>
       <c r="G155" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H155" s="2">
         <v>30</v>
       </c>
       <c r="I155" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J155" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K155" s="2" t="s">
         <v>15</v>
@@ -6268,13 +6226,13 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D156" s="2">
         <v>549</v>
@@ -6303,34 +6261,34 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D157" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="E157" s="2">
-        <v>783</v>
+        <v>478</v>
       </c>
       <c r="F157" s="2">
-        <v>-164</v>
+        <v>146</v>
       </c>
       <c r="G157" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H157" s="2">
         <v>30</v>
       </c>
       <c r="I157" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J157" s="5" t="s">
-        <v>82</v>
+        <v>-10</v>
+      </c>
+      <c r="J157" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K157" s="2" t="s">
         <v>15</v>
@@ -6341,31 +6299,31 @@
         <v>116</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="D158" s="2">
-        <v>624</v>
+        <v>413</v>
       </c>
       <c r="E158" s="2">
         <v>783</v>
       </c>
       <c r="F158" s="2">
-        <v>-159</v>
+        <v>-370</v>
       </c>
       <c r="G158" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H158" s="2">
         <v>30</v>
       </c>
       <c r="I158" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J158" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
+      </c>
+      <c r="J158" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K158" s="2" t="s">
         <v>15</v>
@@ -6373,31 +6331,31 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="D159" s="2">
-        <v>549</v>
+        <v>413</v>
       </c>
       <c r="E159" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F159" s="2">
-        <v>-309</v>
+        <v>-370</v>
       </c>
       <c r="G159" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H159" s="2">
         <v>30</v>
       </c>
       <c r="I159" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J159" s="3" t="s">
         <v>14</v>
@@ -6408,34 +6366,34 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D160" s="2">
-        <v>622</v>
+        <v>549</v>
       </c>
       <c r="E160" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F160" s="2">
-        <v>-236</v>
+        <v>-234</v>
       </c>
       <c r="G160" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H160" s="2">
         <v>30</v>
       </c>
       <c r="I160" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J160" s="5" t="s">
-        <v>82</v>
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K160" s="2" t="s">
         <v>15</v>
@@ -6446,28 +6404,28 @@
         <v>117</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D161" s="2">
-        <v>641</v>
+        <v>413</v>
       </c>
       <c r="E161" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F161" s="2">
-        <v>-217</v>
+        <v>-370</v>
       </c>
       <c r="G161" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H161" s="2">
         <v>30</v>
       </c>
       <c r="I161" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J161" s="3" t="s">
         <v>14</v>
@@ -6478,806 +6436,36 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="D162" s="2">
-        <v>534</v>
+        <v>413</v>
       </c>
       <c r="E162" s="2">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="F162" s="2">
-        <v>-324</v>
+        <v>-370</v>
       </c>
       <c r="G162" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H162" s="2">
         <v>30</v>
       </c>
       <c r="I162" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J162" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
+      </c>
+      <c r="J162" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D163" s="2">
-        <v>569</v>
-      </c>
-      <c r="E163" s="2">
-        <v>858</v>
-      </c>
-      <c r="F163" s="2">
-        <v>-289</v>
-      </c>
-      <c r="G163" s="2">
-        <v>46</v>
-      </c>
-      <c r="H163" s="2">
-        <v>30</v>
-      </c>
-      <c r="I163" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J163" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K163" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A164" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D164" s="2">
-        <v>622</v>
-      </c>
-      <c r="E164" s="2">
-        <v>858</v>
-      </c>
-      <c r="F164" s="2">
-        <v>-236</v>
-      </c>
-      <c r="G164" s="2">
-        <v>46</v>
-      </c>
-      <c r="H164" s="2">
-        <v>30</v>
-      </c>
-      <c r="I164" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J164" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K164" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A165" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D165" s="2">
-        <v>414</v>
-      </c>
-      <c r="E165" s="2">
-        <v>783</v>
-      </c>
-      <c r="F165" s="2">
-        <v>-369</v>
-      </c>
-      <c r="G165" s="2">
-        <v>20</v>
-      </c>
-      <c r="H165" s="2">
-        <v>30</v>
-      </c>
-      <c r="I165" s="2">
-        <v>10</v>
-      </c>
-      <c r="J165" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K165" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A166" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D166" s="2">
-        <v>549</v>
-      </c>
-      <c r="E166" s="2">
-        <v>783</v>
-      </c>
-      <c r="F166" s="2">
-        <v>-234</v>
-      </c>
-      <c r="G166" s="2">
-        <v>30</v>
-      </c>
-      <c r="H166" s="2">
-        <v>30</v>
-      </c>
-      <c r="I166" s="2">
-        <v>0</v>
-      </c>
-      <c r="J166" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K166" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A167" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D167" s="2">
-        <v>641</v>
-      </c>
-      <c r="E167" s="2">
-        <v>783</v>
-      </c>
-      <c r="F167" s="2">
-        <v>-142</v>
-      </c>
-      <c r="G167" s="2">
-        <v>40</v>
-      </c>
-      <c r="H167" s="2">
-        <v>30</v>
-      </c>
-      <c r="I167" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J167" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K167" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A168" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D168" s="2">
-        <v>624</v>
-      </c>
-      <c r="E168" s="2">
-        <v>478</v>
-      </c>
-      <c r="F168" s="2">
-        <v>146</v>
-      </c>
-      <c r="G168" s="2">
-        <v>40</v>
-      </c>
-      <c r="H168" s="2">
-        <v>30</v>
-      </c>
-      <c r="I168" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J168" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K168" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A169" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D169" s="2">
-        <v>624</v>
-      </c>
-      <c r="E169" s="2">
-        <v>478</v>
-      </c>
-      <c r="F169" s="2">
-        <v>146</v>
-      </c>
-      <c r="G169" s="2">
-        <v>40</v>
-      </c>
-      <c r="H169" s="2">
-        <v>30</v>
-      </c>
-      <c r="I169" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J169" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K169" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A170" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D170" s="2">
-        <v>414</v>
-      </c>
-      <c r="E170" s="2">
-        <v>783</v>
-      </c>
-      <c r="F170" s="2">
-        <v>-369</v>
-      </c>
-      <c r="G170" s="2">
-        <v>20</v>
-      </c>
-      <c r="H170" s="2">
-        <v>30</v>
-      </c>
-      <c r="I170" s="2">
-        <v>10</v>
-      </c>
-      <c r="J170" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K170" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A171" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D171" s="2">
-        <v>414</v>
-      </c>
-      <c r="E171" s="2">
-        <v>783</v>
-      </c>
-      <c r="F171" s="2">
-        <v>-369</v>
-      </c>
-      <c r="G171" s="2">
-        <v>20</v>
-      </c>
-      <c r="H171" s="2">
-        <v>30</v>
-      </c>
-      <c r="I171" s="2">
-        <v>10</v>
-      </c>
-      <c r="J171" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K171" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A172" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D172" s="2">
-        <v>549</v>
-      </c>
-      <c r="E172" s="2">
-        <v>783</v>
-      </c>
-      <c r="F172" s="2">
-        <v>-234</v>
-      </c>
-      <c r="G172" s="2">
-        <v>30</v>
-      </c>
-      <c r="H172" s="2">
-        <v>30</v>
-      </c>
-      <c r="I172" s="2">
-        <v>0</v>
-      </c>
-      <c r="J172" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K172" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A173" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D173" s="2">
-        <v>624</v>
-      </c>
-      <c r="E173" s="2">
-        <v>478</v>
-      </c>
-      <c r="F173" s="2">
-        <v>146</v>
-      </c>
-      <c r="G173" s="2">
-        <v>40</v>
-      </c>
-      <c r="H173" s="2">
-        <v>30</v>
-      </c>
-      <c r="I173" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J173" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K173" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A174" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D174" s="2">
-        <v>624</v>
-      </c>
-      <c r="E174" s="2">
-        <v>478</v>
-      </c>
-      <c r="F174" s="2">
-        <v>146</v>
-      </c>
-      <c r="G174" s="2">
-        <v>40</v>
-      </c>
-      <c r="H174" s="2">
-        <v>30</v>
-      </c>
-      <c r="I174" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J174" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K174" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A175" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D175" s="2">
-        <v>414</v>
-      </c>
-      <c r="E175" s="2">
-        <v>783</v>
-      </c>
-      <c r="F175" s="2">
-        <v>-369</v>
-      </c>
-      <c r="G175" s="2">
-        <v>20</v>
-      </c>
-      <c r="H175" s="2">
-        <v>30</v>
-      </c>
-      <c r="I175" s="2">
-        <v>10</v>
-      </c>
-      <c r="J175" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K175" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A176" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D176" s="2">
-        <v>414</v>
-      </c>
-      <c r="E176" s="2">
-        <v>783</v>
-      </c>
-      <c r="F176" s="2">
-        <v>-369</v>
-      </c>
-      <c r="G176" s="2">
-        <v>20</v>
-      </c>
-      <c r="H176" s="2">
-        <v>30</v>
-      </c>
-      <c r="I176" s="2">
-        <v>10</v>
-      </c>
-      <c r="J176" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K176" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A177" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D177" s="2">
-        <v>549</v>
-      </c>
-      <c r="E177" s="2">
-        <v>783</v>
-      </c>
-      <c r="F177" s="2">
-        <v>-234</v>
-      </c>
-      <c r="G177" s="2">
-        <v>30</v>
-      </c>
-      <c r="H177" s="2">
-        <v>30</v>
-      </c>
-      <c r="I177" s="2">
-        <v>0</v>
-      </c>
-      <c r="J177" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K177" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A178" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D178" s="2">
-        <v>624</v>
-      </c>
-      <c r="E178" s="2">
-        <v>478</v>
-      </c>
-      <c r="F178" s="2">
-        <v>146</v>
-      </c>
-      <c r="G178" s="2">
-        <v>40</v>
-      </c>
-      <c r="H178" s="2">
-        <v>30</v>
-      </c>
-      <c r="I178" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J178" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K178" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A179" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D179" s="2">
-        <v>624</v>
-      </c>
-      <c r="E179" s="2">
-        <v>478</v>
-      </c>
-      <c r="F179" s="2">
-        <v>146</v>
-      </c>
-      <c r="G179" s="2">
-        <v>40</v>
-      </c>
-      <c r="H179" s="2">
-        <v>30</v>
-      </c>
-      <c r="I179" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J179" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K179" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A180" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D180" s="2">
-        <v>624</v>
-      </c>
-      <c r="E180" s="2">
-        <v>478</v>
-      </c>
-      <c r="F180" s="2">
-        <v>146</v>
-      </c>
-      <c r="G180" s="2">
-        <v>40</v>
-      </c>
-      <c r="H180" s="2">
-        <v>30</v>
-      </c>
-      <c r="I180" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J180" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K180" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A181" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D181" s="2">
-        <v>414</v>
-      </c>
-      <c r="E181" s="2">
-        <v>783</v>
-      </c>
-      <c r="F181" s="2">
-        <v>-369</v>
-      </c>
-      <c r="G181" s="2">
-        <v>20</v>
-      </c>
-      <c r="H181" s="2">
-        <v>30</v>
-      </c>
-      <c r="I181" s="2">
-        <v>10</v>
-      </c>
-      <c r="J181" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K181" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A182" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D182" s="2">
-        <v>414</v>
-      </c>
-      <c r="E182" s="2">
-        <v>783</v>
-      </c>
-      <c r="F182" s="2">
-        <v>-369</v>
-      </c>
-      <c r="G182" s="2">
-        <v>20</v>
-      </c>
-      <c r="H182" s="2">
-        <v>30</v>
-      </c>
-      <c r="I182" s="2">
-        <v>10</v>
-      </c>
-      <c r="J182" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K182" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A183" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D183" s="2">
-        <v>622</v>
-      </c>
-      <c r="E183" s="2">
-        <v>783</v>
-      </c>
-      <c r="F183" s="2">
-        <v>-161</v>
-      </c>
-      <c r="G183" s="2">
-        <v>46</v>
-      </c>
-      <c r="H183" s="2">
-        <v>30</v>
-      </c>
-      <c r="I183" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J183" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K183" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A184" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D184" s="2">
-        <v>624</v>
-      </c>
-      <c r="E184" s="2">
-        <v>478</v>
-      </c>
-      <c r="F184" s="2">
-        <v>146</v>
-      </c>
-      <c r="G184" s="2">
-        <v>40</v>
-      </c>
-      <c r="H184" s="2">
-        <v>30</v>
-      </c>
-      <c r="I184" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J184" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K184" s="2" t="s">
         <v>15</v>
       </c>
     </row>
